--- a/docs/matrice-roles-direx.xlsx
+++ b/docs/matrice-roles-direx.xlsx
@@ -2270,9 +2270,9 @@
           <t xml:space="preserve">V</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">AMV</t>
+      <c r="G15" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FULL</t>
         </is>
       </c>
       <c r="H15" t="inlineStr" s="3">
@@ -2285,14 +2285,14 @@
           <t xml:space="preserve">V</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">V</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">AMV</t>
+      <c r="J15" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FULL</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FULL</t>
         </is>
       </c>
       <c r="L15" t="inlineStr" s="5">
@@ -2310,14 +2310,14 @@
           <t xml:space="preserve">V</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">V</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">AMV</t>
+      <c r="O15" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FULL</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FULL</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr" s="5">
@@ -2335,14 +2335,14 @@
           <t xml:space="preserve">V</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr" s="0">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr" s="0">
-        <is>
-          <t xml:space="preserve"/>
+      <c r="T15" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FULL</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FULL</t>
         </is>
       </c>
       <c r="V15" t="inlineStr" s="0">
@@ -2355,14 +2355,14 @@
           <t xml:space="preserve">V</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr" s="0">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr" s="0">
-        <is>
-          <t xml:space="preserve"/>
+      <c r="X15" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FULL</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FULL</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr" s="0">
@@ -2422,9 +2422,9 @@
           <t xml:space="preserve">V</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">AMV</t>
+      <c r="G16" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FULL</t>
         </is>
       </c>
       <c r="H16" t="inlineStr" s="5">
@@ -2437,14 +2437,14 @@
           <t xml:space="preserve">V</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">V</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">V</t>
+      <c r="J16" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FULL</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FULL</t>
         </is>
       </c>
       <c r="L16" t="inlineStr" s="5">
@@ -2462,14 +2462,14 @@
           <t xml:space="preserve">V</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">V</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">V</t>
+      <c r="O16" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FULL</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FULL</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr" s="5">
@@ -2487,14 +2487,14 @@
           <t xml:space="preserve">V</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">V</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">V</t>
+      <c r="T16" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FULL</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FULL</t>
         </is>
       </c>
       <c r="V16" t="inlineStr" s="5">
@@ -2507,14 +2507,14 @@
           <t xml:space="preserve">V</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">V</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">V</t>
+      <c r="X16" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FULL</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FULL</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr" s="5">
@@ -2594,9 +2594,9 @@
           <t xml:space="preserve">AMV</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">V</t>
+      <c r="K17" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">AMV</t>
         </is>
       </c>
       <c r="L17" t="inlineStr" s="5">
@@ -2619,9 +2619,9 @@
           <t xml:space="preserve">AMV</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">V</t>
+      <c r="P17" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">AMV</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr" s="5">
@@ -2898,9 +2898,9 @@
           <t xml:space="preserve">AMV</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">V</t>
+      <c r="K19" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">AMV</t>
         </is>
       </c>
       <c r="L19" t="inlineStr" s="5">
@@ -2923,9 +2923,9 @@
           <t xml:space="preserve">AMV</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">V</t>
+      <c r="P19" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">AMV</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr" s="5">
@@ -4094,9 +4094,9 @@
           <t xml:space="preserve">V</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">V</t>
+      <c r="G27" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">AMV</t>
         </is>
       </c>
       <c r="H27" t="inlineStr" s="5">
@@ -4114,9 +4114,9 @@
           <t xml:space="preserve">AMV</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">V</t>
+      <c r="K27" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">AMV</t>
         </is>
       </c>
       <c r="L27" t="inlineStr" s="5">
@@ -4139,9 +4139,9 @@
           <t xml:space="preserve">AMV</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">V</t>
+      <c r="P27" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">AMV</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr" s="5">
@@ -4261,14 +4261,14 @@
           <t xml:space="preserve">V</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">V</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">AMV</t>
+      <c r="J28" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ALL</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ALL</t>
         </is>
       </c>
       <c r="L28" t="inlineStr" s="5">
@@ -4286,14 +4286,14 @@
           <t xml:space="preserve">V</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">V</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">AMV</t>
+      <c r="O28" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ALL</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ALL</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr" s="5">
@@ -4702,9 +4702,9 @@
           <t xml:space="preserve">V</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">V</t>
+      <c r="G31" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">AMV</t>
         </is>
       </c>
       <c r="H31" t="inlineStr" s="3">
@@ -6982,9 +6982,9 @@
           <t xml:space="preserve">V</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">V</t>
+      <c r="G46" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">AMV</t>
         </is>
       </c>
       <c r="H46" t="inlineStr" s="5">
@@ -7052,9 +7052,9 @@
           <t xml:space="preserve">AMV</t>
         </is>
       </c>
-      <c r="U46" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">V</t>
+      <c r="U46" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">AMV</t>
         </is>
       </c>
       <c r="V46" t="inlineStr" s="5">
@@ -7072,9 +7072,9 @@
           <t xml:space="preserve">AMV</t>
         </is>
       </c>
-      <c r="Y46" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">V</t>
+      <c r="Y46" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">AMV</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr" s="5">
@@ -8118,37 +8118,49 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr" s="6">
+      <c r="A6" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FULL</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">Tout ALL, plus SUPPRIMER (D) — abris et morgues des LOG / OPS des PC et de l'Anim</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr" s="6">
         <is>
           <t xml:space="preserve">*</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr" s="0">
+      <c r="B7" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">Super Administrateur : tout</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr" s="0">
+    <row r="8">
+      <c r="A8" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">(vide)</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr" s="0">
+      <c r="B8" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">Aucun droit</t>
         </is>
       </c>
     </row>
-    <row r="8"/>
-    <row r="9">
-      <c r="A9" t="inlineStr" s="0">
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">Lecture</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr" s="0">
+      <c r="B10" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">Grille de DÉPART (ADR 0022, profil « direx ») : chaque poste part du rôle actuel le plus proche puis reçoit ses écarts ; à corriger cellule par cellule.</t>
         </is>

--- a/docs/matrice-roles-direx.xlsx
+++ b/docs/matrice-roles-direx.xlsx
@@ -3942,9 +3942,9 @@
           <t xml:space="preserve">V</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">V</t>
+      <c r="G26" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">AMV</t>
         </is>
       </c>
       <c r="H26" t="inlineStr" s="5">
@@ -3962,9 +3962,9 @@
           <t xml:space="preserve">AMV</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">V</t>
+      <c r="K26" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">AMV</t>
         </is>
       </c>
       <c r="L26" t="inlineStr" s="5">
@@ -3987,9 +3987,9 @@
           <t xml:space="preserve">AMV</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">V</t>
+      <c r="P26" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">AMV</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr" s="5">
@@ -4002,19 +4002,19 @@
           <t xml:space="preserve">V</t>
         </is>
       </c>
-      <c r="S26" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">V</t>
-        </is>
-      </c>
-      <c r="T26" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">V</t>
-        </is>
-      </c>
-      <c r="U26" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">V</t>
+      <c r="S26" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">AMV</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">AMV</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">AMV</t>
         </is>
       </c>
       <c r="V26" t="inlineStr" s="5">
@@ -4022,19 +4022,19 @@
           <t xml:space="preserve">V</t>
         </is>
       </c>
-      <c r="W26" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">V</t>
-        </is>
-      </c>
-      <c r="X26" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">V</t>
-        </is>
-      </c>
-      <c r="Y26" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">V</t>
+      <c r="W26" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">AMV</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">AMV</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">AMV</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr" s="5">
@@ -7242,7 +7242,7 @@
       </c>
       <c r="F4" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
@@ -7306,7 +7306,7 @@
       </c>
       <c r="F6" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">tous (ADR 0027)</t>
         </is>
       </c>
     </row>
@@ -7370,7 +7370,7 @@
       </c>
       <c r="F8" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">FAR</t>
+          <t xml:space="preserve">tous (ADR 0027)</t>
         </is>
       </c>
     </row>
@@ -7402,7 +7402,7 @@
       </c>
       <c r="F9" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">FAR</t>
+          <t xml:space="preserve">tous (ADR 0027)</t>
         </is>
       </c>
     </row>
@@ -7434,7 +7434,7 @@
       </c>
       <c r="F10" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">tous (ADR 0027)</t>
         </is>
       </c>
     </row>
@@ -7530,7 +7530,7 @@
       </c>
       <c r="F13" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">DGSN, DGPC, FA, gendarmerie</t>
+          <t xml:space="preserve">tous (ADR 0027)</t>
         </is>
       </c>
     </row>
@@ -7562,7 +7562,7 @@
       </c>
       <c r="F14" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">DGSN, DGPC, FA, gendarmerie</t>
+          <t xml:space="preserve">tous (ADR 0027)</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="F15" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">tous (ADR 0027)</t>
         </is>
       </c>
     </row>
@@ -7690,7 +7690,7 @@
       </c>
       <c r="F18" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">tous (ADR 0027)</t>
         </is>
       </c>
     </row>
@@ -7722,7 +7722,7 @@
       </c>
       <c r="F19" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">tous (ADR 0027)</t>
         </is>
       </c>
     </row>
@@ -7754,7 +7754,7 @@
       </c>
       <c r="F20" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">tous (ADR 0027)</t>
         </is>
       </c>
     </row>
@@ -7818,7 +7818,7 @@
       </c>
       <c r="F22" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">tous (ADR 0027)</t>
         </is>
       </c>
     </row>
@@ -7850,7 +7850,7 @@
       </c>
       <c r="F23" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">tous (ADR 0027)</t>
         </is>
       </c>
     </row>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="F24" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">tous (ADR 0027)</t>
         </is>
       </c>
     </row>
